--- a/data/trending_integrated_20260921_13.xlsx
+++ b/data/trending_integrated_20260921_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G2" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203811819035</v>
+        <v>203842194785</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 시사주간지 타임 선정 '세계 최고 헬스테크 기업' 선정으로 인한 주가 급등. 긍정적 전망.</t>
+          <t>미국 타임지 선정 '세계 최고 헬스테크 기업' 그룹 선정 소식 기반 주가 급등. 10방 뉴스 및 쩜상 기대감. 단기 반등 후 재하락 가능성 경고.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스카이랩스', '헬스테크', '선정']</t>
+          <t>['헬스테크', '타임지 선정', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10820</v>
+        <v>10810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.96%</t>
+          <t>'+19.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G3" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>230567581770</v>
+        <v>232321613445</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>후공정 대장주로 부각되며 강한 거래대금 동반 상승. 내년 전망 기대.</t>
+          <t>SFA반도체의 강한 거래대금 동반 상승 및 후공정 대장주로서의 지위 부각. 전고점 돌파 및 내년 실적 기대감. 5만 원 목표 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['후공정', '대장주', '거래대금']</t>
+          <t>['후공정', '거래대금', '실적 전망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20200</v>
+        <v>20550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.37%</t>
+          <t>'+11.26%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>78735780670</v>
+        <v>82547225220</v>
       </c>
       <c r="P4" t="n">
         <v>21600</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>연기금 입성 및 신규 호재 기대감, 키트루다 능가 삼중항체 개발로 상승 전망.</t>
+          <t>연기금 입성 및 ADC 확장 관련 기대감. 보유자 영역 진입 가능성 언급. 단기 급등 후 급락 가능성 및 좋은 뉴스 부재에 대한 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['연기금', '삼중항체', '상승']</t>
+          <t>['연기금', 'ADC', '보유자 영역']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32300</v>
+        <v>32400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.94%</t>
+          <t>'+9.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F5" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G5" t="n">
-        <v>1872</v>
+        <v>1951</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>29484745550</v>
+        <v>30761264300</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 관련 논란 지속. 조건부 수용 및 담관암 임상 실패 가능성 제기, 투자자 불안감 고조.</t>
+          <t>미국 FDA 신약 승인 관련 불확실성 및 과거 CRL 사례 언급. 담관암 임상 결과에 대한 의문 제기. 외국인 매도와 개미 매수 패턴 지적.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA', '신약승인', '담관암']</t>
+          <t>['FDA 승인', '담관암', 'CRL']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5870</v>
+        <v>11390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.10%</t>
+          <t>'+8.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>158</v>
+        <v>364</v>
       </c>
       <c r="H6" t="n">
-        <v>0.19</v>
+        <v>18.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5430</v>
+        <v>10520</v>
       </c>
       <c r="K6" t="n">
-        <v>5710</v>
+        <v>10780</v>
       </c>
       <c r="L6" t="n">
-        <v>6280</v>
+        <v>12190</v>
       </c>
       <c r="M6" t="n">
-        <v>5600</v>
+        <v>10590</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>60234943185</v>
+        <v>192550188890</v>
       </c>
       <c r="P6" t="n">
-        <v>13140</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>3725</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>-344000</v>
+        <v>-6000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
+          <t>미국 광통신주 급등에 따른 영향 기대. 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['비트코인', '공매도', '신한투자증권']</t>
+          <t>['광통신', '공시', '추세']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11270</v>
+        <v>5860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.13%</t>
+          <t>'+7.92%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>356</v>
+        <v>160</v>
       </c>
       <c r="H7" t="n">
-        <v>18.29</v>
+        <v>0.19</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10520</v>
+        <v>5430</v>
       </c>
       <c r="K7" t="n">
-        <v>10780</v>
+        <v>5710</v>
       </c>
       <c r="L7" t="n">
-        <v>12190</v>
+        <v>6280</v>
       </c>
       <c r="M7" t="n">
-        <v>10590</v>
+        <v>5600</v>
       </c>
       <c r="N7" t="n">
-        <v>18.13</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>190683479215</v>
+        <v>60440399705</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>13140</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>3725</v>
       </c>
       <c r="R7" t="n">
-        <v>-6000</v>
+        <v>-344000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 영향 기대. 공시 가능성 언급.</t>
+          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '공시', '추세']</t>
+          <t>['비트코인', '공매도', '신한투자증권']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>208500</v>
+        <v>209000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.32%</t>
+          <t>'+6.58%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="H8" t="n">
         <v>75.44</v>
@@ -1153,7 +1153,7 @@
         <v>199800</v>
       </c>
       <c r="L8" t="n">
-        <v>208500</v>
+        <v>209000</v>
       </c>
       <c r="M8" t="n">
         <v>199600</v>
@@ -1162,7 +1162,7 @@
         <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>600275348050</v>
+        <v>623045559800</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G9" t="n">
-        <v>2869</v>
+        <v>2860</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3910402437500</v>
+        <v>4040375339750</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신한증권 시스템 오류 논란 속 외인 매수세 유입. HBM 경쟁 및 3분기 실적 발표 기대감.</t>
+          <t>신한증권 전산 오류 속 외인 매수세 유입 및 HBM 관련 기대감. BNK 증권 목표가 하향 조정. 배당락 고려 시점.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HBM', '배당금', '자사주소각']</t>
+          <t>['외인 매수', 'HBM', '배당']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1877000</v>
+        <v>1875000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.08%</t>
+          <t>'+0.97%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G10" t="n">
-        <v>2240</v>
+        <v>2217</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3097168950000</v>
+        <v>3188832092000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>신한증권 시스템 오류로 거래 불편. 엔비디아 등 해외 반도체주 강세에 따른 상승 기대감.</t>
+          <t>신한증권 전산 오류 속 SK하이닉스 주가 상승 기대감. HBM 관련 ETF 대란 언급. 200만원 돌파 가능성 및 전강후강 패턴 예상.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '수출', '호가창']</t>
+          <t>['HBM', 'ETF', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13690</v>
+        <v>26550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.30%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>338</v>
+        <v>154</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>2.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13870</v>
+        <v>26800</v>
       </c>
       <c r="K11" t="n">
-        <v>14070</v>
+        <v>27400</v>
       </c>
       <c r="L11" t="n">
-        <v>14790</v>
+        <v>27750</v>
       </c>
       <c r="M11" t="n">
-        <v>13610</v>
+        <v>25650</v>
       </c>
       <c r="N11" t="n">
-        <v>4.92</v>
+        <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>63592234290</v>
+        <v>115548433475</v>
       </c>
       <c r="P11" t="n">
-        <v>30200</v>
+        <v>59600</v>
       </c>
       <c r="Q11" t="n">
-        <v>3540</v>
+        <v>1030</v>
       </c>
       <c r="R11" t="n">
-        <v>-298000</v>
+        <v>-234000</v>
       </c>
       <c r="S11" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['AI', '광통신', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26400</v>
+        <v>13680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.49%</t>
+          <t>'-1.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3</v>
+        <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>149</v>
+        <v>340</v>
       </c>
       <c r="H12" t="n">
-        <v>2.11</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26800</v>
+        <v>13870</v>
       </c>
       <c r="K12" t="n">
-        <v>27400</v>
+        <v>14070</v>
       </c>
       <c r="L12" t="n">
-        <v>27750</v>
+        <v>14790</v>
       </c>
       <c r="M12" t="n">
-        <v>25650</v>
+        <v>13610</v>
       </c>
       <c r="N12" t="n">
-        <v>2.41</v>
+        <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>114448041075</v>
+        <v>63931278830</v>
       </c>
       <c r="P12" t="n">
-        <v>59600</v>
+        <v>30200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1030</v>
+        <v>3540</v>
       </c>
       <c r="R12" t="n">
-        <v>-234000</v>
+        <v>-298000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '목표가']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F13" t="n">
         <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>67974854995</v>
+        <v>68566620480</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 장부 조작 의혹 제기 및 대차해지 운동 독려. 추세 상승 기대.</t>
+          <t>공매도 장부 조작 및 대차 부족 의혹 제기, 주가 상승 억제 움직임에 대한 불만 표출. 대차 해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '추세']</t>
+          <t>['공매도', '대차 해지', '주가 조작']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77800</v>
+        <v>77900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F14" t="n">
         <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="H14" t="n">
         <v>10.58</v>
@@ -1714,7 +1714,7 @@
         <v>10.68</v>
       </c>
       <c r="O14" t="n">
-        <v>97004694550</v>
+        <v>98099582500</v>
       </c>
       <c r="P14" t="n">
         <v>184000</v>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유럽 드론 시장 확대에 따른 K-방산 수혜 기대. 공매도 청산 및 10만원 돌파 가능성.</t>
+          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17630</v>
+        <v>17710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.77%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F15" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G15" t="n">
-        <v>973</v>
+        <v>1008</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>193306713735</v>
+        <v>196427681035</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4055</v>
+        <v>4060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.91%</t>
+          <t>'-3.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>93</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="H16" t="n">
         <v>0.33</v>
@@ -1898,7 +1898,7 @@
         <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>29763311547</v>
+        <v>29920182546</v>
       </c>
       <c r="P16" t="n">
         <v>6480</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주요 재료 소멸 및 거래량 부진으로 인한 주가 하락세. 코인 및 메타버스 관련주 대비 낮은 투자 매력.</t>
+          <t>재료 소멸 및 주가 하락 전망. 물량 넘기기 의혹과 함께 신규 및 기존 투자자에게 매수 금지 권고. 5일선 하향 돌파.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['재료소멸', '거래량', '개잡주']</t>
+          <t>['재료 소멸', '물량 넘기기', '주가 전망']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29950</v>
+        <v>313000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-4.28%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.48</v>
+        <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G17" t="n">
-        <v>163</v>
+        <v>237</v>
       </c>
       <c r="H17" t="n">
-        <v>11.92</v>
+        <v>3.62</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>31450</v>
+        <v>327000</v>
       </c>
       <c r="K17" t="n">
-        <v>31500</v>
+        <v>324000</v>
       </c>
       <c r="L17" t="n">
-        <v>31550</v>
+        <v>340500</v>
       </c>
       <c r="M17" t="n">
-        <v>29900</v>
+        <v>308500</v>
       </c>
       <c r="N17" t="n">
-        <v>11.44</v>
+        <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>77812934600</v>
+        <v>80004333000</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>635000</v>
       </c>
       <c r="Q17" t="n">
-        <v>15000</v>
+        <v>52600</v>
       </c>
       <c r="R17" t="n">
-        <v>-420000</v>
+        <v>-52000</v>
       </c>
       <c r="S17" t="n">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대한전선 주가 하락세 지속. 반도체 섹터 순환매 기대감 있으나 투자자 불만 고조.</t>
+          <t>52주 신고가 돌파 시도. 40만원 돌파 및 고평가 논란.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['반도체', '순환매', '낙폭']</t>
+          <t>['신고가', '고평가', '돌파']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>311000</v>
+        <v>30050</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.89%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.66</v>
+        <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>237</v>
+        <v>167</v>
       </c>
       <c r="H18" t="n">
-        <v>3.62</v>
+        <v>11.92</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>327000</v>
+        <v>31450</v>
       </c>
       <c r="K18" t="n">
-        <v>324000</v>
+        <v>31500</v>
       </c>
       <c r="L18" t="n">
-        <v>340500</v>
+        <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>308500</v>
+        <v>29900</v>
       </c>
       <c r="N18" t="n">
-        <v>1.96</v>
+        <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>79329880000</v>
+        <v>79266884250</v>
       </c>
       <c r="P18" t="n">
-        <v>635000</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>52600</v>
+        <v>15000</v>
       </c>
       <c r="R18" t="n">
-        <v>-52000</v>
+        <v>-420000</v>
       </c>
       <c r="S18" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 시도. 40만원 돌파 및 고평가 논란.</t>
+          <t>주가 하락세에 대한 답답함과 피로감. IR 담당자 및 회사 운영에 대한 불만. 추석 연휴 전 추가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['신고가', '고평가', '돌파']</t>
+          <t>['주가 하락', 'IR 담당자', '추세']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28400</v>
+        <v>28250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-24.06%</t>
+          <t>'-24.47%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>733</v>
+        <v>747</v>
       </c>
       <c r="F19" t="n">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="G19" t="n">
-        <v>1387</v>
+        <v>1416</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>106429969300</v>
+        <v>108311273275</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>임상 2상 결과 및 빅파마 협력 기대감에도 불구하고 주가 하한가 기록. 투자자 투매 심리 작용.</t>
+          <t>임상 2상 결과 및 글로벌 빅파마 협상 관련 불확실성. 하한가 반복 및 투자자 손실 우려. 바이오주 투기 심리 비판.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상2상', '하한가', '바이오']</t>
+          <t>['임상 2상', '하한가', '바이오주']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_13.xlsx
+++ b/data/trending_integrated_20260921_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F2" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203842194785</v>
+        <v>203880423285</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10810</v>
+        <v>10880</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.84%</t>
+          <t>'+20.62%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,7 +673,7 @@
         <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" t="n">
         <v>225</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>232321613445</v>
+        <v>234284805175</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SFA반도체의 강한 거래대금 동반 상승 및 후공정 대장주로서의 지위 부각. 전고점 돌파 및 내년 실적 기대감. 5만 원 목표 제시.</t>
+          <t>후공정 대장주로서의 강한 상승세 및 연이은 상한가 기록. 올해보다 내년 실적 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['후공정', '거래대금', '실적 전망']</t>
+          <t>['후공정', '상한가', '거래대금']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20550</v>
+        <v>20700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.26%</t>
+          <t>'+12.07%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>82547225220</v>
+        <v>84573389195</v>
       </c>
       <c r="P4" t="n">
         <v>21600</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>연기금 입성 및 ADC 확장 관련 기대감. 보유자 영역 진입 가능성 언급. 단기 급등 후 급락 가능성 및 좋은 뉴스 부재에 대한 우려.</t>
+          <t>연기금 입성 및 삼중항체 개발 기대감. 보유자 영역 진입 및 급등 후 급락 가능성 경고.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['연기금', 'ADC', '보유자 영역']</t>
+          <t>['연기금', '삼중항체', '보유자 영역']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32400</v>
+        <v>32550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.27%</t>
+          <t>'+9.78%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="F5" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G5" t="n">
-        <v>1951</v>
+        <v>2052</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>30761264300</v>
+        <v>32209582700</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 FDA 신약 승인 관련 불확실성 및 과거 CRL 사례 언급. 담관암 임상 결과에 대한 의문 제기. 외국인 매도와 개미 매수 패턴 지적.</t>
+          <t>FDA 신약 승인 관련 상반된 정보와 기대감 속에 외국인 매도 및 개미 매수 패턴 지속, 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암', 'CRL']</t>
+          <t>['FDA', '신약 승인', '리보세라닙']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11390</v>
+        <v>5850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.27%</t>
+          <t>'+7.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.16</v>
+        <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>364</v>
+        <v>170</v>
       </c>
       <c r="H6" t="n">
-        <v>18.29</v>
+        <v>0.19</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10520</v>
+        <v>5430</v>
       </c>
       <c r="K6" t="n">
-        <v>10780</v>
+        <v>5710</v>
       </c>
       <c r="L6" t="n">
-        <v>12190</v>
+        <v>6280</v>
       </c>
       <c r="M6" t="n">
-        <v>10590</v>
+        <v>5600</v>
       </c>
       <c r="N6" t="n">
-        <v>18.13</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>192550188890</v>
+        <v>60628582710</v>
       </c>
       <c r="P6" t="n">
-        <v>22450</v>
+        <v>13140</v>
       </c>
       <c r="Q6" t="n">
-        <v>1760</v>
+        <v>3725</v>
       </c>
       <c r="R6" t="n">
-        <v>-6000</v>
+        <v>-344000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 영향 기대. 공시 가능성 언급.</t>
+          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '공시', '추세']</t>
+          <t>['비트코인', '공매도', '신한투자증권']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5860</v>
+        <v>11290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.92%</t>
+          <t>'+7.32%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.31</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>160</v>
+        <v>390</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19</v>
+        <v>18.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5430</v>
+        <v>10520</v>
       </c>
       <c r="K7" t="n">
-        <v>5710</v>
+        <v>10780</v>
       </c>
       <c r="L7" t="n">
-        <v>6280</v>
+        <v>12190</v>
       </c>
       <c r="M7" t="n">
-        <v>5600</v>
+        <v>10590</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>18.13</v>
       </c>
       <c r="O7" t="n">
-        <v>60440399705</v>
+        <v>195983582820</v>
       </c>
       <c r="P7" t="n">
-        <v>13140</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>3725</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>-344000</v>
+        <v>-6000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
+          <t>미국 광통신주 급등 및 나스닥 선물 호조에 따른 기대감. 공시 임박 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['비트코인', '공매도', '신한투자증권']</t>
+          <t>['광통신주', '나스닥 선물', '공시']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>209000</v>
+        <v>208500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.58%</t>
+          <t>'+6.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" t="n">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="H8" t="n">
         <v>75.44</v>
@@ -1162,7 +1162,7 @@
         <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>623045559800</v>
+        <v>631198657300</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>274000</v>
+        <v>274250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.98%</t>
+          <t>'+5.08%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G9" t="n">
-        <v>2860</v>
+        <v>2836</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4040375339750</v>
+        <v>4141921833500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신한증권 전산 오류 속 외인 매수세 유입 및 HBM 관련 기대감. BNK 증권 목표가 하향 조정. 배당락 고려 시점.</t>
+          <t>추석 전 3만원 돌파 기대감과 3분기 잠정실적 발표 및 자사주 소각/배당 이벤트 언급. 일부 증권사 목표가 하향 조정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 매수', 'HBM', '배당']</t>
+          <t>['목표가', '잠정실적', '자사주 소각']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1875000</v>
+        <v>1878000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.97%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G10" t="n">
-        <v>2217</v>
+        <v>2241</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3188832092000</v>
+        <v>3275470173000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>신한증권 전산 오류 속 SK하이닉스 주가 상승 기대감. HBM 관련 ETF 대란 언급. 200만원 돌파 가능성 및 전강후강 패턴 예상.</t>
+          <t>신한증권 전산 오류로 인한 거래 불편 호소. HBM 경쟁력 및 193만 돌파 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HBM', 'ETF', '반도체']</t>
+          <t>['HBM', '신한증권', '호가창']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1412,7 +1412,7 @@
         <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>115548433475</v>
+        <v>116202243000</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13680</v>
+        <v>13660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.37%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H12" t="n">
         <v>5.5</v>
@@ -1530,7 +1530,7 @@
         <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>63931278830</v>
+        <v>64444369650</v>
       </c>
       <c r="P12" t="n">
         <v>30200</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18520</v>
+        <v>78100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>379</v>
+        <v>733</v>
       </c>
       <c r="H13" t="n">
-        <v>10.74</v>
+        <v>10.58</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18910</v>
+        <v>80000</v>
       </c>
       <c r="K13" t="n">
-        <v>19050</v>
+        <v>82900</v>
       </c>
       <c r="L13" t="n">
-        <v>19050</v>
+        <v>83000</v>
       </c>
       <c r="M13" t="n">
-        <v>18090</v>
+        <v>75300</v>
       </c>
       <c r="N13" t="n">
-        <v>10.74</v>
+        <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>68566620480</v>
+        <v>99185495000</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>184000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>44750</v>
       </c>
       <c r="R13" t="n">
-        <v>-673000</v>
+        <v>-499000</v>
       </c>
       <c r="S13" t="n">
-        <v>-88000</v>
+        <v>-56000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 장부 조작 및 대차 부족 의혹 제기, 주가 상승 억제 움직임에 대한 불만 표출. 대차 해지 운동 촉구.</t>
+          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '대차 해지', '주가 조작']</t>
+          <t>['드론', 'K-방산', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77900</v>
+        <v>18420</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>725</v>
+        <v>388</v>
       </c>
       <c r="H14" t="n">
-        <v>10.58</v>
+        <v>10.74</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>80000</v>
+        <v>18910</v>
       </c>
       <c r="K14" t="n">
-        <v>82900</v>
+        <v>19050</v>
       </c>
       <c r="L14" t="n">
-        <v>83000</v>
+        <v>19050</v>
       </c>
       <c r="M14" t="n">
-        <v>75300</v>
+        <v>18090</v>
       </c>
       <c r="N14" t="n">
-        <v>10.68</v>
+        <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>98099582500</v>
+        <v>69592352920</v>
       </c>
       <c r="P14" t="n">
-        <v>184000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>44750</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-499000</v>
+        <v>-673000</v>
       </c>
       <c r="S14" t="n">
-        <v>-56000</v>
+        <v>-88000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
+          <t>공매도 세력과의 갈등 심화 및 대차해지 운동 동참 호소. 주가 상승 압력 및 추가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['드론', 'K-방산', '공매도']</t>
+          <t>['공매도', '대차해지', '주가 상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17710</v>
+        <v>17665</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-3.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F15" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G15" t="n">
-        <v>1008</v>
+        <v>1023</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>196427681035</v>
+        <v>198165361625</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등 수혜 기대감 속 기관 매수세 유입. 투자주의 종목 지정 및 CB 영향 고려.</t>
+          <t>미국 광통신 AI주 급등 및 나스닥 선물 호조 수혜 기대. 기관 매수세 유입 및 투자 주의 요인 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '기관매수']</t>
+          <t>['광통신', 'AI주', '기관 매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4060</v>
+        <v>4065</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.79%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="H16" t="n">
         <v>0.33</v>
@@ -1898,7 +1898,7 @@
         <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>29920182546</v>
+        <v>30137639186</v>
       </c>
       <c r="P16" t="n">
         <v>6480</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>재료 소멸 및 주가 하락 전망. 물량 넘기기 의혹과 함께 신규 및 기존 투자자에게 매수 금지 권고. 5일선 하향 돌파.</t>
+          <t>재료 대비 주가 부진 및 고점 매물대 형성. 신규 및 물타기 금지, 가격 레벨 다운.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['재료 소멸', '물량 넘기기', '주가 전망']</t>
+          <t>['재료', '개잡주', '물량 넘기기']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,7 +1958,7 @@
         <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F17" t="n">
         <v>77</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>80004333000</v>
+        <v>80617375500</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2056,7 +2056,7 @@
         <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H18" t="n">
         <v>11.92</v>
@@ -2082,7 +2082,7 @@
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>79266884250</v>
+        <v>79886319150</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락세에 대한 답답함과 피로감. IR 담당자 및 회사 운영에 대한 불만. 추석 연휴 전 추가 하락 가능성 언급.</t>
+          <t>금요일 매도 후 추가 하락에 대한 우려 및 28000원 복귀 실패 가능성 언급. IR 담당자 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 하락', 'IR 담당자', '추세']</t>
+          <t>['하락', '매도', 'IR 담당자']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28250</v>
+        <v>27900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-24.47%</t>
+          <t>'-25.40%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="F19" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G19" t="n">
-        <v>1416</v>
+        <v>1491</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>108311273275</v>
+        <v>109563621775</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>임상 2상 결과 및 글로벌 빅파마 협상 관련 불확실성. 하한가 반복 및 투자자 손실 우려. 바이오주 투기 심리 비판.</t>
+          <t>제2임상시험 결과 발표 후 하한가 기록 및 추가 하한가 우려. 바이오 투자에 대한 이해 부족 지적.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상 2상', '하한가', '바이오주']</t>
+          <t>['임상시험', '하한가', '바이오']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_13.xlsx
+++ b/data/trending_integrated_20260921_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203880423285</v>
+        <v>203907769035</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -619,7 +619,7 @@
         <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>114000</v>
+        <v>137000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10880</v>
+        <v>10820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.62%</t>
+          <t>'+19.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
         <v>68</v>
       </c>
       <c r="G3" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>234284805175</v>
+        <v>236465741450</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -711,23 +711,23 @@
         <v>3735</v>
       </c>
       <c r="R3" t="n">
-        <v>405000</v>
+        <v>521000</v>
       </c>
       <c r="S3" t="n">
-        <v>52000</v>
+        <v>59000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>후공정 대장주로서의 강한 상승세 및 연이은 상한가 기록. 올해보다 내년 실적 기대감.</t>
+          <t>강한 거래대금 동반하며 상승 중, 전고점 돌파 및 5만원, 2만원 목표 기대. 올해보다 내년 전망 긍정적.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['후공정', '상한가', '거래대금']</t>
+          <t>['강한 거래대금', '전고점 돌파', '내년 전망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20700</v>
+        <v>20800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.07%</t>
+          <t>'+12.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>84573389195</v>
+        <v>85884167920</v>
       </c>
       <c r="P4" t="n">
         <v>21600</v>
@@ -803,14 +803,14 @@
         <v>9900</v>
       </c>
       <c r="R4" t="n">
-        <v>53000</v>
+        <v>1000</v>
       </c>
       <c r="S4" t="n">
-        <v>6000</v>
+        <v>43000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>연기금 입성 및 삼중항체 개발 기대감. 보유자 영역 진입 및 급등 후 급락 가능성 경고.</t>
+          <t>연기금 입성 및 ADC 확장 관련 언급. 21000원 도달 기대감 및 머크 인증 기반 10만원 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['연기금', '삼중항체', '보유자 영역']</t>
+          <t>['연기금 입성', 'ADC 확장', '머크 인증']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32550</v>
+        <v>32900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.78%</t>
+          <t>'+10.96%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="F5" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G5" t="n">
-        <v>2052</v>
+        <v>2107</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>32209582700</v>
+        <v>34635023900</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -895,23 +895,23 @@
         <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-148000</v>
+        <v>-192000</v>
       </c>
       <c r="S5" t="n">
         <v>-7000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 관련 상반된 정보와 기대감 속에 외국인 매도 및 개미 매수 패턴 지속, 급락 가능성 언급.</t>
+          <t>FDA 신약 승인 기대감 속 리라푸그라티닙 NDA 승인 언급. 외인 매도 및 개미 매수 횡보, 급락 확률 높다는 의견.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA', '신약 승인', '리보세라닙']</t>
+          <t>['FDA 신약 승인', 'NDA 승인', '외인 매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5850</v>
+        <v>11310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.73%</t>
+          <t>'+7.51%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>400</v>
       </c>
       <c r="H6" t="n">
-        <v>0.19</v>
+        <v>18.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5430</v>
+        <v>10520</v>
       </c>
       <c r="K6" t="n">
-        <v>5710</v>
+        <v>10780</v>
       </c>
       <c r="L6" t="n">
-        <v>6280</v>
+        <v>12190</v>
       </c>
       <c r="M6" t="n">
-        <v>5600</v>
+        <v>10590</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>60628582710</v>
+        <v>197789967970</v>
       </c>
       <c r="P6" t="n">
-        <v>13140</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>3725</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>-344000</v>
+        <v>-70000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
+          <t>11500 돌파 시 고점 돌파 전망 및 공시 기대감. 다만, 오후 폭락 조심 의견.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['비트코인', '공매도', '신한투자증권']</t>
+          <t>['고점 돌파', '공시 기대', '폭락 조심']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11290</v>
+        <v>5820</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.32%</t>
+          <t>'+7.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>390</v>
+        <v>176</v>
       </c>
       <c r="H7" t="n">
-        <v>18.29</v>
+        <v>0.19</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10520</v>
+        <v>5430</v>
       </c>
       <c r="K7" t="n">
-        <v>10780</v>
+        <v>5710</v>
       </c>
       <c r="L7" t="n">
-        <v>12190</v>
+        <v>6280</v>
       </c>
       <c r="M7" t="n">
-        <v>10590</v>
+        <v>5600</v>
       </c>
       <c r="N7" t="n">
-        <v>18.13</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>195983582820</v>
+        <v>60897574440</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>13140</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>3725</v>
       </c>
       <c r="R7" t="n">
-        <v>-6000</v>
+        <v>-345000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등 및 나스닥 선물 호조에 따른 기대감. 공시 임박 가능성 언급.</t>
+          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신주', '나스닥 선물', '공시']</t>
+          <t>['비트코인', '공매도', '신한투자증권']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>208500</v>
+        <v>209000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.32%</t>
+          <t>'+6.58%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="H8" t="n">
         <v>75.44</v>
@@ -1162,7 +1162,7 @@
         <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>631198657300</v>
+        <v>641043986050</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1171,10 +1171,10 @@
         <v>64700</v>
       </c>
       <c r="R8" t="n">
-        <v>504000</v>
+        <v>652000</v>
       </c>
       <c r="S8" t="n">
-        <v>-25000</v>
+        <v>-2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G9" t="n">
-        <v>2836</v>
+        <v>2893</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1245,7 +1245,7 @@
         <v>264000</v>
       </c>
       <c r="L9" t="n">
-        <v>274500</v>
+        <v>275000</v>
       </c>
       <c r="M9" t="n">
         <v>263500</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4141921833500</v>
+        <v>4316215045000</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1263,23 +1263,23 @@
         <v>81100</v>
       </c>
       <c r="R9" t="n">
-        <v>3622000</v>
+        <v>5146000</v>
       </c>
       <c r="S9" t="n">
-        <v>391000</v>
+        <v>1095000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>추석 전 3만원 돌파 기대감과 3분기 잠정실적 발표 및 자사주 소각/배당 이벤트 언급. 일부 증권사 목표가 하향 조정.</t>
+          <t>27000원 돌파 및 30000원 기대감. 외인 매수세 유입 및 3분기 잠정 실적 발표, 자사주 소각 및 배당 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['목표가', '잠정실적', '자사주 소각']</t>
+          <t>['외인 매수', '실적 발표', '자사주 소각']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1878000</v>
+        <v>1877000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+1.08%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G10" t="n">
-        <v>2241</v>
+        <v>2246</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3275470173000</v>
+        <v>3376595897000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1355,14 +1355,14 @@
         <v>333000</v>
       </c>
       <c r="R10" t="n">
-        <v>-64000</v>
+        <v>-62000</v>
       </c>
       <c r="S10" t="n">
-        <v>91000</v>
+        <v>139000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>신한증권 전산 오류로 인한 거래 불편 호소. HBM 경쟁력 및 193만 돌파 기대감.</t>
+          <t>반도체 수출 잠정치 및 193만 돌파 시 로켓 불기둥 기대. 신한증권 전산 오류에 대한 불만.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HBM', '신한증권', '호가창']</t>
+          <t>['반도체 수출', '로켓 불기둥', '전산 오류']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,123 +1391,123 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26550</v>
+        <v>18375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-1.21%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>160</v>
+        <v>404</v>
       </c>
       <c r="H11" t="n">
-        <v>2.11</v>
+        <v>10.74</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>26800</v>
+        <v>18600</v>
       </c>
       <c r="K11" t="n">
-        <v>27400</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>25650</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.41</v>
+        <v>10.74</v>
       </c>
       <c r="O11" t="n">
-        <v>116202243000</v>
+        <v>70637000000</v>
       </c>
       <c r="P11" t="n">
-        <v>59600</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-234000</v>
+        <v>-698000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-184000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
+          <t>공매도 관련 내용 언급 및 대차 해지 운동 독려. 주가 상승 추세 기대감 있으나, 이유 없는 하락 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '목표가']</t>
+          <t>['공매도', '대차 해지', '주가 상승']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13660</v>
+        <v>26450</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58</v>
+        <v>-0.3</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>345</v>
+        <v>174</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>2.11</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13870</v>
+        <v>26800</v>
       </c>
       <c r="K12" t="n">
-        <v>14070</v>
+        <v>27400</v>
       </c>
       <c r="L12" t="n">
-        <v>14790</v>
+        <v>27750</v>
       </c>
       <c r="M12" t="n">
-        <v>13610</v>
+        <v>25650</v>
       </c>
       <c r="N12" t="n">
-        <v>4.92</v>
+        <v>2.41</v>
       </c>
       <c r="O12" t="n">
-        <v>64444369650</v>
+        <v>117051995450</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>59600</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>1030</v>
       </c>
       <c r="R12" t="n">
-        <v>-298000</v>
+        <v>-234000</v>
       </c>
       <c r="S12" t="n">
-        <v>-7000</v>
+        <v>-37000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['AI', '광통신', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,130 +1568,130 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78100</v>
+        <v>13630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-1.73%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>0.58</v>
       </c>
       <c r="E13" t="n">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>733</v>
+        <v>348</v>
       </c>
       <c r="H13" t="n">
-        <v>10.58</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>80000</v>
+        <v>13870</v>
       </c>
       <c r="K13" t="n">
-        <v>82900</v>
+        <v>14070</v>
       </c>
       <c r="L13" t="n">
-        <v>83000</v>
+        <v>14790</v>
       </c>
       <c r="M13" t="n">
-        <v>75300</v>
+        <v>13610</v>
       </c>
       <c r="N13" t="n">
-        <v>10.68</v>
+        <v>4.92</v>
       </c>
       <c r="O13" t="n">
-        <v>99185495000</v>
+        <v>65450958070</v>
       </c>
       <c r="P13" t="n">
-        <v>184000</v>
+        <v>30200</v>
       </c>
       <c r="Q13" t="n">
-        <v>44750</v>
+        <v>3540</v>
       </c>
       <c r="R13" t="n">
-        <v>-499000</v>
+        <v>-306000</v>
       </c>
       <c r="S13" t="n">
-        <v>-56000</v>
+        <v>-8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['드론', 'K-방산', '공매도']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18420</v>
+        <v>77900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.59%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>388</v>
+        <v>732</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74</v>
+        <v>10.58</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18910</v>
+        <v>80000</v>
       </c>
       <c r="K14" t="n">
-        <v>19050</v>
+        <v>82900</v>
       </c>
       <c r="L14" t="n">
-        <v>19050</v>
+        <v>83000</v>
       </c>
       <c r="M14" t="n">
-        <v>18090</v>
+        <v>75300</v>
       </c>
       <c r="N14" t="n">
-        <v>10.74</v>
+        <v>10.68</v>
       </c>
       <c r="O14" t="n">
-        <v>69592352920</v>
+        <v>100524108100</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>184000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>44750</v>
       </c>
       <c r="R14" t="n">
-        <v>-673000</v>
+        <v>-556000</v>
       </c>
       <c r="S14" t="n">
-        <v>-88000</v>
+        <v>-46000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 세력과의 갈등 심화 및 대차해지 운동 동참 호소. 주가 상승 압력 및 추가 하락 가능성 언급.</t>
+          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '주가 상승']</t>
+          <t>['드론', 'K-방산', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17665</v>
+        <v>4075</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.58%</t>
+          <t>'-3.44%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.29</v>
+        <v>-0.22</v>
       </c>
       <c r="E15" t="n">
-        <v>221</v>
+        <v>94</v>
       </c>
       <c r="F15" t="n">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>1023</v>
+        <v>373</v>
       </c>
       <c r="H15" t="n">
-        <v>7.9</v>
+        <v>0.33</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18320</v>
+        <v>4220</v>
       </c>
       <c r="K15" t="n">
-        <v>18450</v>
+        <v>4220</v>
       </c>
       <c r="L15" t="n">
-        <v>18590</v>
+        <v>4415</v>
       </c>
       <c r="M15" t="n">
-        <v>17590</v>
+        <v>4030</v>
       </c>
       <c r="N15" t="n">
-        <v>4.61</v>
+        <v>0.55</v>
       </c>
       <c r="O15" t="n">
-        <v>198165361625</v>
+        <v>30380526802</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>6480</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>1738</v>
       </c>
       <c r="R15" t="n">
-        <v>-1480000</v>
+        <v>242000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 AI주 급등 및 나스닥 선물 호조 수혜 기대. 기관 매수세 유입 및 투자 주의 요인 언급.</t>
+          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', 'AI주', '기관 매수']</t>
+          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4065</v>
+        <v>17680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-3.49%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.22</v>
+        <v>3.29</v>
       </c>
       <c r="E16" t="n">
-        <v>95</v>
+        <v>228</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="G16" t="n">
-        <v>381</v>
+        <v>1041</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33</v>
+        <v>7.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4220</v>
+        <v>18320</v>
       </c>
       <c r="K16" t="n">
-        <v>4220</v>
+        <v>18450</v>
       </c>
       <c r="L16" t="n">
-        <v>4415</v>
+        <v>18590</v>
       </c>
       <c r="M16" t="n">
-        <v>4030</v>
+        <v>17590</v>
       </c>
       <c r="N16" t="n">
-        <v>0.55</v>
+        <v>4.61</v>
       </c>
       <c r="O16" t="n">
-        <v>30137639186</v>
+        <v>199461529585</v>
       </c>
       <c r="P16" t="n">
-        <v>6480</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>1738</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>208000</v>
+        <v>-1730000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>재료 대비 주가 부진 및 고점 매물대 형성. 신규 및 물타기 금지, 가격 레벨 다운.</t>
+          <t>미국 광통신 AI주 급등 및 나스닥 선물 호조 수혜 기대. 기관 매수세 유입 및 투자 주의 요인 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['재료', '개잡주', '물량 넘기기']</t>
+          <t>['광통신', 'AI주', '기관 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
         <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F17" t="n">
         <v>77</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>80617375500</v>
+        <v>81173046250</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -1999,7 +1999,7 @@
         <v>52600</v>
       </c>
       <c r="R17" t="n">
-        <v>-52000</v>
+        <v>-62000</v>
       </c>
       <c r="S17" t="n">
         <v>-2000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30050</v>
+        <v>29900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-4.93%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G18" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H18" t="n">
         <v>11.92</v>
@@ -2076,13 +2076,13 @@
         <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>29900</v>
+        <v>29850</v>
       </c>
       <c r="N18" t="n">
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>79886319150</v>
+        <v>83424948375</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2091,23 +2091,23 @@
         <v>15000</v>
       </c>
       <c r="R18" t="n">
-        <v>-420000</v>
+        <v>-662000</v>
       </c>
       <c r="S18" t="n">
-        <v>-8000</v>
+        <v>-9000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>금요일 매도 후 추가 하락에 대한 우려 및 28000원 복귀 실패 가능성 언급. IR 담당자 비판.</t>
+          <t>매수세 및 매도세 혼재, 3만원 이상 유지 어려움 언급. 징글징글한 흐름에 대한 부정적 의견.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['하락', '매도', 'IR 담당자']</t>
+          <t>['매수세', '매도세', '주가 유지']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27900</v>
+        <v>27800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-25.40%</t>
+          <t>'-25.67%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>756</v>
+        <v>772</v>
       </c>
       <c r="F19" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="G19" t="n">
-        <v>1491</v>
+        <v>1526</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>109563621775</v>
+        <v>111824534875</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2183,23 +2183,23 @@
         <v>26200</v>
       </c>
       <c r="R19" t="n">
-        <v>163000</v>
+        <v>218000</v>
       </c>
       <c r="S19" t="n">
-        <v>30000</v>
+        <v>-23000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>제2임상시험 결과 발표 후 하한가 기록 및 추가 하한가 우려. 바이오 투자에 대한 이해 부족 지적.</t>
+          <t>본장 하한가 풀릴 듯한 매도 물량 언급. 임상 시험 결과 불확실성 및 깡통 바이오 등극 우려. 결국 하한가 예상.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상시험', '하한가', '바이오']</t>
+          <t>['매도 물량', '임상 시험', '하한가']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_13.xlsx
+++ b/data/trending_integrated_20260921_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F2" t="n">
         <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203907769035</v>
+        <v>203941174785</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10820</v>
+        <v>10870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.96%</t>
+          <t>'+20.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>236465741450</v>
+        <v>238676008395</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>강한 거래대금 동반하며 상승 중, 전고점 돌파 및 5만원, 2만원 목표 기대. 올해보다 내년 전망 긍정적.</t>
+          <t>강한 거래대금 동반하며 전고점 돌파 기대. 후공정 대장주로서 2만 및 5만 목표.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['강한 거래대금', '전고점 돌파', '내년 전망']</t>
+          <t>['거래대금', '후공정', '대장주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20800</v>
+        <v>20750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.62%</t>
+          <t>'+12.34%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>85884167920</v>
+        <v>86906853520</v>
       </c>
       <c r="P4" t="n">
         <v>21600</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>연기금 입성 및 ADC 확장 관련 언급. 21000원 도달 기대감 및 머크 인증 기반 10만원 상승 전망.</t>
+          <t>머크 인증 기반 10만원 돌파 기대감. ADC 확장 및 제2의 박셀바이오 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['연기금 입성', 'ADC 확장', '머크 인증']</t>
+          <t>['ADC', '머크', '기대감']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32900</v>
+        <v>32250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.96%</t>
+          <t>'+8.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F5" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="G5" t="n">
-        <v>2107</v>
+        <v>2144</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>34635023900</v>
+        <v>36694400300</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 기대감 속 리라푸그라티닙 NDA 승인 언급. 외인 매도 및 개미 매수 횡보, 급락 확률 높다는 의견.</t>
+          <t>FDA 신약 승인 기대감 속 투자 주의. 리보세라닙 NDA 통과 및 리픽투 관련 논란.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA 신약 승인', 'NDA 승인', '외인 매도']</t>
+          <t>['FDA', 'NDA', '리보세라닙']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11310</v>
+        <v>5850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.51%</t>
+          <t>'+7.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.16</v>
+        <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>400</v>
+        <v>177</v>
       </c>
       <c r="H6" t="n">
-        <v>18.29</v>
+        <v>0.19</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10520</v>
+        <v>5430</v>
       </c>
       <c r="K6" t="n">
-        <v>10780</v>
+        <v>5710</v>
       </c>
       <c r="L6" t="n">
-        <v>12190</v>
+        <v>6280</v>
       </c>
       <c r="M6" t="n">
-        <v>10590</v>
+        <v>5600</v>
       </c>
       <c r="N6" t="n">
-        <v>18.13</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>197789967970</v>
+        <v>61105436170</v>
       </c>
       <c r="P6" t="n">
-        <v>22450</v>
+        <v>13140</v>
       </c>
       <c r="Q6" t="n">
-        <v>1760</v>
+        <v>3725</v>
       </c>
       <c r="R6" t="n">
-        <v>-70000</v>
+        <v>-345000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>11500 돌파 시 고점 돌파 전망 및 공시 기대감. 다만, 오후 폭락 조심 의견.</t>
+          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['고점 돌파', '공시 기대', '폭락 조심']</t>
+          <t>['비트코인', '공매도', '신한투자증권']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5820</v>
+        <v>11240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.18%</t>
+          <t>'+6.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.31</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
-        <v>176</v>
+        <v>424</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19</v>
+        <v>18.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5430</v>
+        <v>10520</v>
       </c>
       <c r="K7" t="n">
-        <v>5710</v>
+        <v>10780</v>
       </c>
       <c r="L7" t="n">
-        <v>6280</v>
+        <v>12190</v>
       </c>
       <c r="M7" t="n">
-        <v>5600</v>
+        <v>10590</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>18.13</v>
       </c>
       <c r="O7" t="n">
-        <v>60897574440</v>
+        <v>199393845660</v>
       </c>
       <c r="P7" t="n">
-        <v>13140</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>3725</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>-345000</v>
+        <v>-70000</v>
       </c>
       <c r="S7" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
+          <t>광통신주 급등 및 연기금 매수세 유입. 공시 기대감 속 11500원 돌파 및 2만원 목표.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['비트코인', '공매도', '신한투자증권']</t>
+          <t>['광통신', '연기금', '공시']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>209000</v>
+        <v>208500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.58%</t>
+          <t>'+6.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="H8" t="n">
         <v>75.44</v>
@@ -1162,7 +1162,7 @@
         <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>641043986050</v>
+        <v>653048708800</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자우, 배당 기대감 속 주가 상승 전망. 자사주 취득 및 소각, 외인 매수세 유입 가능성 언급.</t>
+          <t>자사주 소각 및 배당 기대감 속 30만원 돌파 전망. 우선주 집중 매수세 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당', '자사주', '외인']</t>
+          <t>['자사주', '배당', '우선주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G9" t="n">
-        <v>2893</v>
+        <v>2788</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4316215045000</v>
+        <v>4386114527000</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>27000원 돌파 및 30000원 기대감. 외인 매수세 유입 및 3분기 잠정 실적 발표, 자사주 소각 및 배당 관련 언급.</t>
+          <t>BNK증권 목표가 27만원 하향 조정 및 외인 매수세 유입. HBM 경쟁력 및 3분기 실적 발표 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 매수', '실적 발표', '자사주 소각']</t>
+          <t>['HBM', '실적', '외인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G10" t="n">
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3376595897000</v>
+        <v>3469688870500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1391,123 +1391,123 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18375</v>
+        <v>26450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.21%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>404</v>
+        <v>179</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74</v>
+        <v>2.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18600</v>
+        <v>26800</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>27400</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>25650</v>
       </c>
       <c r="N11" t="n">
-        <v>10.74</v>
+        <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>70637000000</v>
+        <v>117788535025</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>59600</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="R11" t="n">
-        <v>-698000</v>
+        <v>-234000</v>
       </c>
       <c r="S11" t="n">
-        <v>-184000</v>
+        <v>-37000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>공매도 관련 내용 언급 및 대차 해지 운동 독려. 주가 상승 추세 기대감 있으나, 이유 없는 하락 언급.</t>
+          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '대차 해지', '주가 상승']</t>
+          <t>['AI', '광통신', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26450</v>
+        <v>13630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-1.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3</v>
+        <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>174</v>
+        <v>365</v>
       </c>
       <c r="H12" t="n">
-        <v>2.11</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26800</v>
+        <v>13870</v>
       </c>
       <c r="K12" t="n">
-        <v>27400</v>
+        <v>14070</v>
       </c>
       <c r="L12" t="n">
-        <v>27750</v>
+        <v>14790</v>
       </c>
       <c r="M12" t="n">
-        <v>25650</v>
+        <v>13610</v>
       </c>
       <c r="N12" t="n">
-        <v>2.41</v>
+        <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>117051995450</v>
+        <v>66014257485</v>
       </c>
       <c r="P12" t="n">
-        <v>59600</v>
+        <v>30200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1030</v>
+        <v>3540</v>
       </c>
       <c r="R12" t="n">
-        <v>-234000</v>
+        <v>-306000</v>
       </c>
       <c r="S12" t="n">
-        <v>-37000</v>
+        <v>-8000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '목표가']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,130 +1568,130 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13630</v>
+        <v>78100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.73%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.58</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="G13" t="n">
-        <v>348</v>
+        <v>736</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>10.58</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13870</v>
+        <v>80000</v>
       </c>
       <c r="K13" t="n">
-        <v>14070</v>
+        <v>82900</v>
       </c>
       <c r="L13" t="n">
-        <v>14790</v>
+        <v>83000</v>
       </c>
       <c r="M13" t="n">
-        <v>13610</v>
+        <v>75300</v>
       </c>
       <c r="N13" t="n">
-        <v>4.92</v>
+        <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>65450958070</v>
+        <v>101507515800</v>
       </c>
       <c r="P13" t="n">
-        <v>30200</v>
+        <v>184000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3540</v>
+        <v>44750</v>
       </c>
       <c r="R13" t="n">
-        <v>-306000</v>
+        <v>-556000</v>
       </c>
       <c r="S13" t="n">
-        <v>-8000</v>
+        <v>-46000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['드론', 'K-방산', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77900</v>
+        <v>18400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-2.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>732</v>
+        <v>410</v>
       </c>
       <c r="H14" t="n">
-        <v>10.58</v>
+        <v>10.74</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>80000</v>
+        <v>18910</v>
       </c>
       <c r="K14" t="n">
-        <v>82900</v>
+        <v>19050</v>
       </c>
       <c r="L14" t="n">
-        <v>83000</v>
+        <v>19050</v>
       </c>
       <c r="M14" t="n">
-        <v>75300</v>
+        <v>18090</v>
       </c>
       <c r="N14" t="n">
-        <v>10.68</v>
+        <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>100524108100</v>
+        <v>71809140910</v>
       </c>
       <c r="P14" t="n">
-        <v>184000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>44750</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-556000</v>
+        <v>-698000</v>
       </c>
       <c r="S14" t="n">
-        <v>-46000</v>
+        <v>-184000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
+          <t>공매도 관련 내용 언급 및 대차 해지 운동 독려. 주가 상승 추세 기대감 있으나, 이유 없는 하락 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['드론', 'K-방산', '공매도']</t>
+          <t>['공매도', '대차 해지', '주가 상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4075</v>
+        <v>17650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.44%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.22</v>
+        <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>232</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="G15" t="n">
-        <v>373</v>
+        <v>1074</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33</v>
+        <v>7.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4220</v>
+        <v>18320</v>
       </c>
       <c r="K15" t="n">
-        <v>4220</v>
+        <v>18450</v>
       </c>
       <c r="L15" t="n">
-        <v>4415</v>
+        <v>18590</v>
       </c>
       <c r="M15" t="n">
-        <v>4030</v>
+        <v>17590</v>
       </c>
       <c r="N15" t="n">
-        <v>0.55</v>
+        <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>30380526802</v>
+        <v>202286236080</v>
       </c>
       <c r="P15" t="n">
-        <v>6480</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>1738</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>242000</v>
+        <v>-1730000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1000</v>
+        <v>-3000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
+          <t>미국 광통신주 급등 및 기관 매수세 유입. 3만원 터치 기대 속 투자주의 종목.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
+          <t>['광통신', '기관', 'AI']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17680</v>
+        <v>314500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.49%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.29</v>
+        <v>1.66</v>
       </c>
       <c r="E16" t="n">
-        <v>228</v>
+        <v>113</v>
       </c>
       <c r="F16" t="n">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="G16" t="n">
-        <v>1041</v>
+        <v>237</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>3.62</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18320</v>
+        <v>327000</v>
       </c>
       <c r="K16" t="n">
-        <v>18450</v>
+        <v>324000</v>
       </c>
       <c r="L16" t="n">
-        <v>18590</v>
+        <v>340500</v>
       </c>
       <c r="M16" t="n">
-        <v>17590</v>
+        <v>308500</v>
       </c>
       <c r="N16" t="n">
-        <v>4.61</v>
+        <v>1.96</v>
       </c>
       <c r="O16" t="n">
-        <v>199461529585</v>
+        <v>82290302250</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>635000</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>52600</v>
       </c>
       <c r="R16" t="n">
-        <v>-1730000</v>
+        <v>-62000</v>
       </c>
       <c r="S16" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신 AI주 급등 및 나스닥 선물 호조 수혜 기대. 기관 매수세 유입 및 투자 주의 요인 언급.</t>
+          <t>52주 신고가 돌파 시도. 40만원 돌파 및 고평가 논란.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', 'AI주', '기관 매수']</t>
+          <t>['신고가', '고평가', '돌파']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>313000</v>
+        <v>29850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.28%</t>
+          <t>'-5.09%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.66</v>
+        <v>0.48</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>237</v>
+        <v>187</v>
       </c>
       <c r="H17" t="n">
-        <v>3.62</v>
+        <v>11.92</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>327000</v>
+        <v>31450</v>
       </c>
       <c r="K17" t="n">
-        <v>324000</v>
+        <v>31500</v>
       </c>
       <c r="L17" t="n">
-        <v>340500</v>
+        <v>31550</v>
       </c>
       <c r="M17" t="n">
-        <v>308500</v>
+        <v>29800</v>
       </c>
       <c r="N17" t="n">
-        <v>1.96</v>
+        <v>11.44</v>
       </c>
       <c r="O17" t="n">
-        <v>81173046250</v>
+        <v>85371313000</v>
       </c>
       <c r="P17" t="n">
-        <v>635000</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>52600</v>
+        <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>-62000</v>
+        <v>-662000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 시도. 40만원 돌파 및 고평가 논란.</t>
+          <t>외인 및 프로그램 매도세 지속, 28000원 복귀 및 급락 가능성. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['신고가', '고평가', '돌파']</t>
+          <t>['매도', '급락', '반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29900</v>
+        <v>4060</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.93%</t>
+          <t>'-10.77%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.48</v>
+        <v>-0.22</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
         <v>56</v>
       </c>
       <c r="G18" t="n">
-        <v>179</v>
+        <v>374</v>
       </c>
       <c r="H18" t="n">
-        <v>11.92</v>
+        <v>0.33</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31450</v>
+        <v>4550</v>
       </c>
       <c r="K18" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>31550</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>29850</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>11.44</v>
+        <v>0.55</v>
       </c>
       <c r="O18" t="n">
-        <v>83424948375</v>
+        <v>30671000000</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-662000</v>
+        <v>242000</v>
       </c>
       <c r="S18" t="n">
-        <v>-9000</v>
+        <v>-1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>매수세 및 매도세 혼재, 3만원 이상 유지 어려움 언급. 징글징글한 흐름에 대한 부정적 의견.</t>
+          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['매수세', '매도세', '주가 유지']</t>
+          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>772</v>
+        <v>785</v>
       </c>
       <c r="F19" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G19" t="n">
-        <v>1526</v>
+        <v>1557</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>111824534875</v>
+        <v>112860128300</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>본장 하한가 풀릴 듯한 매도 물량 언급. 임상 시험 결과 불확실성 및 깡통 바이오 등극 우려. 결국 하한가 예상.</t>
+          <t>임상 시험 결과 불확실성 및 매도 물량 증가. 하한가 풀림 및 바이오 투기 심리 비판.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['매도 물량', '임상 시험', '하한가']</t>
+          <t>['임상', '하한가', '바이오']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_13.xlsx
+++ b/data/trending_integrated_20260921_13.xlsx
@@ -581,10 +581,10 @@
         <v>205</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203941174785</v>
+        <v>203974681535</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10870</v>
+        <v>10830</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.51%</t>
+          <t>'+20.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
         <v>237</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>238676008395</v>
+        <v>240592861130</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,18 +751,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20750</v>
+        <v>20850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.34%</t>
+          <t>'+12.89%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
         <v>54</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>86906853520</v>
+        <v>87773787870</v>
       </c>
       <c r="P4" t="n">
         <v>21600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32250</v>
+        <v>32150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.77%</t>
+          <t>'+8.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="F5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G5" t="n">
-        <v>2144</v>
+        <v>2184</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>36694400300</v>
+        <v>37839445325</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 기대감 속 투자 주의. 리보세라닙 NDA 통과 및 리픽투 관련 논란.</t>
+          <t>미국 FDA 신약 승인 기대감 속 루머성 정보 혼재. 담관암 관련 임상 결과 및 외인 매도 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA', 'NDA', '리보세라닙']</t>
+          <t>['신약 승인', 'FDA', '담관암']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5850</v>
+        <v>11300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.73%</t>
+          <t>'+7.41%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="G6" t="n">
-        <v>177</v>
+        <v>429</v>
       </c>
       <c r="H6" t="n">
-        <v>0.19</v>
+        <v>18.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5430</v>
+        <v>10520</v>
       </c>
       <c r="K6" t="n">
-        <v>5710</v>
+        <v>10780</v>
       </c>
       <c r="L6" t="n">
-        <v>6280</v>
+        <v>12190</v>
       </c>
       <c r="M6" t="n">
-        <v>5600</v>
+        <v>10590</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>61105436170</v>
+        <v>200052308190</v>
       </c>
       <c r="P6" t="n">
-        <v>13140</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>3725</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>-345000</v>
+        <v>-70000</v>
       </c>
       <c r="S6" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
+          <t>광통신주 급등 및 연기금 매수세 유입. 공시 기대감 속 11500원 돌파 및 2만원 목표.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['비트코인', '공매도', '신한투자증권']</t>
+          <t>['광통신', '연기금', '공시']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11240</v>
+        <v>5830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.84%</t>
+          <t>'+7.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>424</v>
+        <v>179</v>
       </c>
       <c r="H7" t="n">
-        <v>18.29</v>
+        <v>0.19</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10520</v>
+        <v>5430</v>
       </c>
       <c r="K7" t="n">
-        <v>10780</v>
+        <v>5710</v>
       </c>
       <c r="L7" t="n">
-        <v>12190</v>
+        <v>6280</v>
       </c>
       <c r="M7" t="n">
-        <v>10590</v>
+        <v>5600</v>
       </c>
       <c r="N7" t="n">
-        <v>18.13</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>199393845660</v>
+        <v>61213729520</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>13140</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>3725</v>
       </c>
       <c r="R7" t="n">
-        <v>-70000</v>
+        <v>-345000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>광통신주 급등 및 연기금 매수세 유입. 공시 기대감 속 11500원 돌파 및 2만원 목표.</t>
+          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '연기금', '공시']</t>
+          <t>['비트코인', '공매도', '신한투자증권']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>208500</v>
+        <v>209000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.32%</t>
+          <t>'+6.58%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="H8" t="n">
         <v>75.44</v>
@@ -1162,7 +1162,7 @@
         <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>653048708800</v>
+        <v>666301929050</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 소각 및 배당 기대감 속 30만원 돌파 전망. 우선주 집중 매수세 유입.</t>
+          <t>외인 수급 집중 및 연말 배당 기대감. 52주 신고가 돌파 및 30만원 목표.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주', '배당', '우선주']</t>
+          <t>['우선주', '외인 수급', '배당 기대']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="G9" t="n">
-        <v>2788</v>
+        <v>2734</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4386114527000</v>
+        <v>4465928479500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>BNK증권 목표가 27만원 하향 조정 및 외인 매수세 유입. HBM 경쟁력 및 3분기 실적 발표 기대.</t>
+          <t>BNK증권 목표가 하향 조정 속 외인 매수세 유입. 3분기 실적 발표 및 자사주 소각/배당 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HBM', '실적', '외인']</t>
+          <t>['외인 매수', '목표가 하향', '자사주 소각']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1877000</v>
+        <v>1874000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.08%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G10" t="n">
-        <v>2249</v>
+        <v>2253</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3469688870500</v>
+        <v>3552382954500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 수출 잠정치 및 193만 돌파 시 로켓 불기둥 기대. 신한증권 전산 오류에 대한 불만.</t>
+          <t>신한증권 시스템 오류 발생 속 반도체 수출 지표 주목. 193만 돌파 및 200만원 이상 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체 수출', '로켓 불기둥', '전산 오류']</t>
+          <t>['반도체 수출', '신한증권 오류', '상승 기대']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26450</v>
+        <v>26350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-1.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>117788535025</v>
+        <v>118916491225</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13630</v>
+        <v>13580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.73%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="H12" t="n">
         <v>5.5</v>
@@ -1524,13 +1524,13 @@
         <v>14790</v>
       </c>
       <c r="M12" t="n">
-        <v>13610</v>
+        <v>13570</v>
       </c>
       <c r="N12" t="n">
         <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>66014257485</v>
+        <v>67698709870</v>
       </c>
       <c r="P12" t="n">
         <v>30200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78100</v>
+        <v>77800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.75%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F13" t="n">
         <v>85</v>
       </c>
       <c r="G13" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="H13" t="n">
         <v>10.58</v>
@@ -1622,7 +1622,7 @@
         <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>101507515800</v>
+        <v>102884163200</v>
       </c>
       <c r="P13" t="n">
         <v>184000</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18400</v>
+        <v>18380</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.70%</t>
+          <t>'-2.80%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>71809140910</v>
+        <v>72855725230</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 관련 내용 언급 및 대차 해지 운동 독려. 주가 상승 추세 기대감 있으나, 이유 없는 하락 언급.</t>
+          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 주가 상승 억제 및 대차해지 운동 주장.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차 해지', '주가 상승']</t>
+          <t>['공매도', '대차해지', '장부 조작']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17650</v>
+        <v>316500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.29</v>
+        <v>1.66</v>
       </c>
       <c r="E15" t="n">
-        <v>232</v>
+        <v>115</v>
       </c>
       <c r="F15" t="n">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="G15" t="n">
-        <v>1074</v>
+        <v>241</v>
       </c>
       <c r="H15" t="n">
-        <v>7.9</v>
+        <v>3.62</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18320</v>
+        <v>327000</v>
       </c>
       <c r="K15" t="n">
-        <v>18450</v>
+        <v>324000</v>
       </c>
       <c r="L15" t="n">
-        <v>18590</v>
+        <v>340500</v>
       </c>
       <c r="M15" t="n">
-        <v>17590</v>
+        <v>308500</v>
       </c>
       <c r="N15" t="n">
-        <v>4.61</v>
+        <v>1.96</v>
       </c>
       <c r="O15" t="n">
-        <v>202286236080</v>
+        <v>84821445500</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>635000</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>52600</v>
       </c>
       <c r="R15" t="n">
-        <v>-1730000</v>
+        <v>-62000</v>
       </c>
       <c r="S15" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등 및 기관 매수세 유입. 3만원 터치 기대 속 투자주의 종목.</t>
+          <t>52주 신고가 돌파 후 주가 등락. 외국인 순매수 유입 속 고평가 논란.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '기관', 'AI']</t>
+          <t>['52주 신고가', '외국인 순매수', '고평가 논란']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>314500</v>
+        <v>4070</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.66</v>
+        <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>237</v>
+        <v>378</v>
       </c>
       <c r="H16" t="n">
-        <v>3.62</v>
+        <v>0.33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>327000</v>
+        <v>4220</v>
       </c>
       <c r="K16" t="n">
-        <v>324000</v>
+        <v>4220</v>
       </c>
       <c r="L16" t="n">
-        <v>340500</v>
+        <v>4415</v>
       </c>
       <c r="M16" t="n">
-        <v>308500</v>
+        <v>4030</v>
       </c>
       <c r="N16" t="n">
-        <v>1.96</v>
+        <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>82290302250</v>
+        <v>30806318742</v>
       </c>
       <c r="P16" t="n">
-        <v>635000</v>
+        <v>6480</v>
       </c>
       <c r="Q16" t="n">
-        <v>52600</v>
+        <v>1738</v>
       </c>
       <c r="R16" t="n">
-        <v>-62000</v>
+        <v>242000</v>
       </c>
       <c r="S16" t="n">
-        <v>-2000</v>
+        <v>-1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 시도. 40만원 돌파 및 고평가 논란.</t>
+          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['신고가', '고평가', '돌파']</t>
+          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29850</v>
+        <v>17650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.09%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.48</v>
+        <v>3.29</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="G17" t="n">
-        <v>187</v>
+        <v>1081</v>
       </c>
       <c r="H17" t="n">
-        <v>11.92</v>
+        <v>7.9</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>31450</v>
+        <v>18320</v>
       </c>
       <c r="K17" t="n">
+        <v>18450</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18590</v>
+      </c>
+      <c r="M17" t="n">
+        <v>17590</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="O17" t="n">
+        <v>203458729380</v>
+      </c>
+      <c r="P17" t="n">
         <v>31500</v>
       </c>
-      <c r="L17" t="n">
-        <v>31550</v>
-      </c>
-      <c r="M17" t="n">
-        <v>29800</v>
-      </c>
-      <c r="N17" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="O17" t="n">
-        <v>85371313000</v>
-      </c>
-      <c r="P17" t="n">
-        <v>75900</v>
-      </c>
       <c r="Q17" t="n">
-        <v>15000</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-662000</v>
+        <v>-1730000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>-3000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외인 및 프로그램 매도세 지속, 28000원 복귀 및 급락 가능성. 투자 심리 위축.</t>
+          <t>미국 광통신주 급등 및 기관 매수세 유입. 3만원 터치 기대 속 투자주의 종목.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['매도', '급락', '반도체']</t>
+          <t>['광통신', '기관', 'AI']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4060</v>
+        <v>29950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.77%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.22</v>
+        <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F18" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>374</v>
+        <v>187</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33</v>
+        <v>11.92</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4550</v>
+        <v>31450</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="N18" t="n">
-        <v>0.55</v>
+        <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>30671000000</v>
+        <v>86629058250</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R18" t="n">
-        <v>242000</v>
+        <v>-662000</v>
       </c>
       <c r="S18" t="n">
-        <v>-1000</v>
+        <v>-9000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
+          <t>외인 및 프로그램 매도세 지속, 28000원 복귀 및 급락 가능성. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
+          <t>['매도', '급락', '반도체']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27800</v>
+        <v>27950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-25.67%</t>
+          <t>'-25.27%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>785</v>
       </c>
       <c r="F19" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G19" t="n">
-        <v>1557</v>
+        <v>1575</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>112860128300</v>
+        <v>113517927050</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>임상 시험 결과 불확실성 및 매도 물량 증가. 하한가 풀림 및 바이오 투기 심리 비판.</t>
+          <t>제2임상시험 결과 및 하한가 기록. 투기성 매매 및 바이오주에 대한 투자 위험성 시사.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상', '하한가', '바이오']</t>
+          <t>['임상시험', '하한가', '바이오주']</t>
         </is>
       </c>
       <c r="X19" t="n">
